--- a/electrocomponents inventory_organized_box.xlsx
+++ b/electrocomponents inventory_organized_box.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmwave\Desktop\share document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB0772-0FBE-4AA5-9F82-B56FB199F161}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54D2B45-B5F7-44AE-9951-75FCCB0F4A01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15396" firstSheet="1" activeTab="3" xr2:uid="{4EF1B334-B9A4-468B-ADB9-1CC422E31F4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15396" firstSheet="3" activeTab="15" xr2:uid="{4EF1B334-B9A4-468B-ADB9-1CC422E31F4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Resistor" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="1067">
   <si>
     <t>connectors</t>
   </si>
@@ -3300,6 +3300,117 @@
   </si>
   <si>
     <t>D-Sub Standard Connectors</t>
+  </si>
+  <si>
+    <t>Diode Schottky zero bias</t>
+  </si>
+  <si>
+    <t>HSMS-2850-TRIG</t>
+  </si>
+  <si>
+    <t>IC DRVR Twisted</t>
+  </si>
+  <si>
+    <t>EL5178ISZ</t>
+  </si>
+  <si>
+    <t>HSMS-2825-BLKG</t>
+  </si>
+  <si>
+    <t>LT1512CS8</t>
+  </si>
+  <si>
+    <t>AA210-25</t>
+  </si>
+  <si>
+    <t>RELAY</t>
+  </si>
+  <si>
+    <t>AQZ102</t>
+  </si>
+  <si>
+    <t>PCAAW-6</t>
+  </si>
+  <si>
+    <t>FMMT2359CT-ND</t>
+  </si>
+  <si>
+    <t>PAT1220-C-5DB-T5</t>
+  </si>
+  <si>
+    <t>PS2012GT2-50-T1</t>
+  </si>
+  <si>
+    <t>RF Power Divider 0-20GHz</t>
+  </si>
+  <si>
+    <t>SKY67159-396LF</t>
+  </si>
+  <si>
+    <t>IC AMP,LNA</t>
+  </si>
+  <si>
+    <t>MOUSER P/N</t>
+  </si>
+  <si>
+    <t>630-ATF-36077-STR</t>
+  </si>
+  <si>
+    <t>MMA712-2012</t>
+  </si>
+  <si>
+    <t>511-1346-ND</t>
+  </si>
+  <si>
+    <t>AEROFLEX/Metlics</t>
+  </si>
+  <si>
+    <t>Emitter IR 850 nm</t>
+  </si>
+  <si>
+    <t>PAT123CT-ND</t>
+  </si>
+  <si>
+    <t>10th order lowpass</t>
+  </si>
+  <si>
+    <t>LTC1569CS8-7</t>
+  </si>
+  <si>
+    <t>SIR-5683T3F</t>
+  </si>
+  <si>
+    <t>SKY12322-86LF</t>
+  </si>
+  <si>
+    <t>AA210-252F</t>
+  </si>
+  <si>
+    <t>UPC-2712TB-E3-A</t>
+  </si>
+  <si>
+    <t>RF detector</t>
+  </si>
+  <si>
+    <t>PE44820B-X</t>
+  </si>
+  <si>
+    <t>Phase shift</t>
+  </si>
+  <si>
+    <t>DRVRSGL</t>
+  </si>
+  <si>
+    <t>Diode Schottky</t>
+  </si>
+  <si>
+    <t>13160-13-F</t>
+  </si>
+  <si>
+    <t>MAX40025CAWT+T</t>
+  </si>
+  <si>
+    <t>IC Comparator</t>
   </si>
 </sst>
 </file>
@@ -4131,8 +4242,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{033C5116-C581-4738-89FD-7C504EF0BCB4}" name="Table11" displayName="Table11" ref="A1:C35" totalsRowShown="0">
-  <autoFilter ref="A1:C35" xr:uid="{F6A91388-09B1-44C6-AC3C-DDCDD2800B36}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{033C5116-C581-4738-89FD-7C504EF0BCB4}" name="Table11" displayName="Table11" ref="A1:C56" totalsRowShown="0">
+  <autoFilter ref="A1:C56" xr:uid="{F6A91388-09B1-44C6-AC3C-DDCDD2800B36}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7D27363D-FE9B-4EAC-A0C0-94634011B7CB}" name="Function"/>
     <tableColumn id="2" xr3:uid="{74CD0856-3C35-4832-BE08-45F70C1843FE}" name="Part Num"/>
@@ -4175,8 +4286,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{726AAC33-7046-4241-BF26-DAC118AB45FD}" name="Table5" displayName="Table5" ref="A1:D78" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:D78" xr:uid="{7E7AB043-6248-4B89-871E-E1E0B44A7144}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{726AAC33-7046-4241-BF26-DAC118AB45FD}" name="Table5" displayName="Table5" ref="A1:D79" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:D79" xr:uid="{7E7AB043-6248-4B89-871E-E1E0B44A7144}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{41E8D986-5302-477C-9717-65347C9B93BC}" name="Filter" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{29F76A88-AC6B-4B4E-9BF9-14C7CEBE500C}" name="NUM" dataDxfId="27"/>
@@ -4215,8 +4326,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{CF7AD01F-A2A9-49C4-B556-9167B10CC447}" name="Table8" displayName="Table8" ref="A1:F31" totalsRowShown="0">
-  <autoFilter ref="A1:F31" xr:uid="{AE52C8EC-0936-4C7A-A36B-61715BA46526}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{CF7AD01F-A2A9-49C4-B556-9167B10CC447}" name="Table8" displayName="Table8" ref="A1:F33" totalsRowShown="0">
+  <autoFilter ref="A1:F33" xr:uid="{AE52C8EC-0936-4C7A-A36B-61715BA46526}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{FCD5F671-EB20-44FA-9894-0D380585B636}" name="Amplifier" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{8745B568-8F2E-4BEE-8CE3-C944E1CE2D1A}" name="package"/>
@@ -8960,7 +9071,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C0893C-FD5A-4DED-A009-611DA139B235}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="17.69921875" customWidth="1"/>
@@ -8994,6 +9105,21 @@
       </c>
       <c r="B4">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -9858,7 +9984,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72C671F-5CD3-4DF8-AF33-1FF838B07D70}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26.796875" customWidth="1"/>
@@ -10045,22 +10171,172 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="2:3">
+    <row r="33" spans="1:3">
       <c r="B33" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
+    <row r="34" spans="1:3">
       <c r="B34" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="35" spans="2:3">
+    <row r="35" spans="1:3">
       <c r="B35" t="s">
         <v>859</v>
       </c>
       <c r="C35">
         <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="B38" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="B39" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="B40" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="B42" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="B43" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="B44" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -12778,7 +13054,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F56564-447C-4AC0-9A0C-F03B4328A463}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.796875" customWidth="1"/>
@@ -13570,6 +13846,16 @@
       </c>
       <c r="C78" s="34"/>
       <c r="D78" s="34"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="34" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D79" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14708,7 +14994,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C7E50B-1E42-4EBB-A787-8899DC26A882}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.296875" customWidth="1"/>
@@ -15069,6 +15355,20 @@
       <c r="F31" t="s">
         <v>1023</v>
       </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="48" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="48" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
